--- a/_report_audit/report.xlsx
+++ b/_report_audit/report.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="106">
   <si>
     <t>Field</t>
   </si>
@@ -33,13 +33,13 @@
     <t>Site Name</t>
   </si>
   <si>
-    <t>Urul site</t>
+    <t>Umbraj</t>
   </si>
   <si>
     <t>Owner</t>
   </si>
   <si>
-    <t>Nikhil salunkhe</t>
+    <t>xyz</t>
   </si>
   <si>
     <t>Owner Mobile</t>
@@ -51,13 +51,13 @@
     <t>Address</t>
   </si>
   <si>
-    <t>urul</t>
+    <t>umbraj</t>
   </si>
   <si>
     <t>City</t>
   </si>
   <si>
-    <t>patan</t>
+    <t>karad</t>
   </si>
   <si>
     <t>State</t>
@@ -69,7 +69,7 @@
     <t>Area</t>
   </si>
   <si>
-    <t>1200 Sq.Ft</t>
+    <t>1700 Sq.Ft</t>
   </si>
   <si>
     <t>Rate per Area</t>
@@ -90,12 +90,15 @@
     <t>Start Date</t>
   </si>
   <si>
-    <t>2026-09-26</t>
+    <t>2026-10-01</t>
   </si>
   <si>
     <t>Expected Completion</t>
   </si>
   <si>
+    <t>2026-12-01</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -162,16 +165,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
-    <t>1st installment Of urul site</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Plinth Level</t>
+    <t>Advance / Booking</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -183,12 +177,12 @@
     <t>Reference</t>
   </si>
   <si>
+    <t>UPI</t>
+  </si>
+  <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>Payment done</t>
-  </si>
-  <si>
     <t>Worker</t>
   </si>
   <si>
@@ -252,15 +246,24 @@
     <t>Invoice No</t>
   </si>
   <si>
-    <t>ultratech</t>
-  </si>
-  <si>
     <t>Cement</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>cement</t>
+  </si>
+  <si>
     <t>Bags</t>
   </si>
   <si>
@@ -276,12 +279,6 @@
     <t>nikhilrs6464@gmail.com</t>
   </si>
   <si>
-    <t>JCB</t>
-  </si>
-  <si>
-    <t>.....</t>
-  </si>
-  <si>
     <t>Workers Present</t>
   </si>
   <si>
@@ -298,15 +295,6 @@
   </si>
   <si>
     <t>Today's Expense</t>
-  </si>
-  <si>
-    <t>measurement of the site area</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
   <si>
     <t>Cost Head</t>
@@ -883,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="4">
-        <v>1920000</v>
+        <v>2720000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -899,7 +887,7 @@
         <v>20</v>
       </c>
       <c r="B12" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -915,103 +903,103 @@
         <v>23</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="5">
-        <v>800000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="5">
-        <v>1120000</v>
+        <v>1020000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5">
-        <v>32000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5">
-        <v>32000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5">
-        <v>69000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5">
-        <v>69000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="5">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="4">
-        <v>1851000</v>
+        <v>2610000</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4">
-        <v>96.41</v>
+        <v>95.96</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1037,80 +1025,54 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>46291</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="9">
-        <v>2</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="10">
-        <v>2000</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1132,41 +1094,41 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B2" s="6">
-        <v>32000</v>
+        <v>45000</v>
       </c>
       <c r="C2" s="6">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="D2" s="6">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B3" s="6">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="C3" s="6">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="D3" s="6">
         <v>0</v>
@@ -1174,13 +1136,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B4" s="6">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="C4" s="6">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="D4" s="6">
         <v>0</v>
@@ -1188,13 +1150,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B5" s="6">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="C5" s="6">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="D5" s="6">
         <v>0</v>
@@ -1202,16 +1164,16 @@
     </row>
     <row r="6" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B6" s="13">
-        <v>69000</v>
+        <v>110000</v>
       </c>
       <c r="C6" s="13">
-        <v>69000</v>
+        <v>105000</v>
       </c>
       <c r="D6" s="13">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -1232,82 +1194,82 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B2" s="6">
-        <v>1920000</v>
+        <v>2720000</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B3" s="6">
-        <v>69000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="14">
-        <v>1851000</v>
+        <v>2610000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="15">
-        <v>96.41</v>
+        <v>95.96</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B6" s="6">
-        <v>800000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6">
-        <v>1120000</v>
+        <v>1020000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B8" s="6">
-        <v>69000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B10" s="6">
-        <v>731000</v>
+        <v>1595000</v>
       </c>
     </row>
   </sheetData>
@@ -1319,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1333,37 +1295,37 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1371,94 +1333,64 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D2" s="6">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="E2" s="6">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="F2" s="6">
         <v>0</v>
       </c>
       <c r="G2" s="7">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="H2" s="7"/>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6">
-        <v>500000</v>
-      </c>
-      <c r="E3" s="6">
-        <v>500000</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>46295</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="10">
-        <v>800000</v>
-      </c>
-      <c r="E4" s="10">
-        <v>800000</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>24</v>
+      <c r="B3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1482,76 +1414,76 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="B2" s="6">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="B3" s="6">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="10">
-        <v>800000</v>
+        <v>1700000</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1577,34 +1509,34 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>18</v>
@@ -1612,16 +1544,16 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" s="6">
         <v>50000</v>
@@ -1630,13 +1562,13 @@
         <v>46291</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I2" s="6">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J2" s="6">
         <v>0</v>
@@ -1647,37 +1579,37 @@
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="10">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I3" s="10">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J3" s="10">
         <v>0</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1689,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1702,66 +1634,98 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>24</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>46296.39475766204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>50000</v>
+      </c>
+      <c r="E2" s="6">
+        <v>50000</v>
+      </c>
+      <c r="F2" s="6">
+        <v>50000</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="7">
+        <v>46296</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="10">
+        <v>50000</v>
+      </c>
+      <c r="F3" s="10">
+        <v>50000</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1773,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1788,37 +1752,37 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>18</v>
@@ -1826,78 +1790,116 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>46291</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
       <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="6">
+        <v>300</v>
+      </c>
+      <c r="H2" s="6">
+        <v>30000</v>
+      </c>
+      <c r="I2" s="6">
+        <v>25000</v>
+      </c>
+      <c r="J2" s="6">
+        <v>5000</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>46296</v>
+      </c>
+      <c r="B3" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="6">
-        <v>320</v>
-      </c>
-      <c r="H2" s="6">
-        <v>32000</v>
-      </c>
-      <c r="I2" s="6">
-        <v>32000</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3">
         <v>50</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="10">
-        <v>32000</v>
-      </c>
-      <c r="I3" s="10">
-        <v>32000</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>24</v>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="6">
+        <v>300</v>
+      </c>
+      <c r="H3" s="6">
+        <v>15000</v>
+      </c>
+      <c r="I3" s="6">
+        <v>15000</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="10">
+        <v>45000</v>
+      </c>
+      <c r="I4" s="10">
+        <v>40000</v>
+      </c>
+      <c r="J4" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1924,48 +1926,48 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1982,22 +1984,22 @@
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="10">
         <v>0</v>
@@ -2032,86 +2034,86 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="6">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="10">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2123,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2137,93 +2139,66 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>46291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="6">
-        <v>5000</v>
-      </c>
-      <c r="E2" s="6">
-        <v>5000</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="10">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="10">
-        <v>5000</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>24</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
